--- a/ig/nr-add-def-ins-collection/ValueSet-fr-core-organization-identifier-type.xlsx
+++ b/ig/nr-add-def-ins-collection/ValueSet-fr-core-organization-identifier-type.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-16T15:07:43+00:00</t>
+    <t>2023-10-23T11:38:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-def-ins-collection/ValueSet-fr-core-organization-identifier-type.xlsx
+++ b/ig/nr-add-def-ins-collection/ValueSet-fr-core-organization-identifier-type.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-23T11:38:46+00:00</t>
+    <t>2023-11-06T10:27:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-def-ins-collection/ValueSet-fr-core-organization-identifier-type.xlsx
+++ b/ig/nr-add-def-ins-collection/ValueSet-fr-core-organization-identifier-type.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-06T10:27:25+00:00</t>
+    <t>2023-11-06T10:34:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-def-ins-collection/ValueSet-fr-core-organization-identifier-type.xlsx
+++ b/ig/nr-add-def-ins-collection/ValueSet-fr-core-organization-identifier-type.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-06T10:34:42+00:00</t>
+    <t>2023-11-06T13:10:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-def-ins-collection/ValueSet-fr-core-organization-identifier-type.xlsx
+++ b/ig/nr-add-def-ins-collection/ValueSet-fr-core-organization-identifier-type.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-06T13:10:33+00:00</t>
+    <t>2023-11-06T13:11:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-def-ins-collection/ValueSet-fr-core-organization-identifier-type.xlsx
+++ b/ig/nr-add-def-ins-collection/ValueSet-fr-core-organization-identifier-type.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-06T13:11:32+00:00</t>
+    <t>2023-11-06T13:13:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-def-ins-collection/ValueSet-fr-core-organization-identifier-type.xlsx
+++ b/ig/nr-add-def-ins-collection/ValueSet-fr-core-organization-identifier-type.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-06T13:13:14+00:00</t>
+    <t>2023-11-06T13:13:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-def-ins-collection/ValueSet-fr-core-organization-identifier-type.xlsx
+++ b/ig/nr-add-def-ins-collection/ValueSet-fr-core-organization-identifier-type.xlsx
@@ -7,7 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from fr-v2-0203" r:id="rId4" sheetId="2"/>
+    <sheet name="Include from FR Core CodeSyst" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.fr/ig/fhir/core/ValueSet/fr-core-organization-identifier-type</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-organization-identifier-type</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-06T13:13:47+00:00</t>
+    <t>2023-11-08T15:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -141,7 +141,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>http://interopsante.org/CodeSystem/fr-v2-0203</t>
+    <t>https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-v2-0203</t>
   </si>
 </sst>
 </file>
